--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -34,22 +34,10 @@
     <t>Shop Total</t>
   </si>
   <si>
-    <t>USD</t>
+    <t xml:space="preserve">Outemu Mechanical Switches for Swappable Keyboards (Pack of 20) </t>
   </si>
   <si>
-    <t>Click Inc HP Switch (Pack of 10)</t>
-  </si>
-  <si>
-    <t>https://stackskb.com/store/click-inc-hp-switch-pack-of-10-pre-order/</t>
-  </si>
-  <si>
-    <t>Free</t>
-  </si>
-  <si>
-    <t>StacksPBT Blank White Cherry Profile Keycaps (113 Key)</t>
-  </si>
-  <si>
-    <t>https://stackskb.com/store/stackspbt-blank-white-cherry-profile-keycaps-113-key/</t>
+    <t>https://www.thecosmicbyte.com/product/outemu-mechanical-switches-for-swappable-keyboards-pack-of-20/?attribute_pa_switch-type=prelubed-brown-switch</t>
   </si>
   <si>
     <t>Gateron Hotswap Sockets</t>
@@ -58,10 +46,19 @@
     <t>https://stackskb.com/store/gateron-hotswap-sockets/</t>
   </si>
   <si>
+    <t>Blank DSA Keycaps (1u) (5n per order)</t>
+  </si>
+  <si>
+    <t>https://meckeys.com/shop/accessories/keyboard-accessories/keycaps/blank/blank-dsa-keycaps-1u/</t>
+  </si>
+  <si>
     <t>TYPE-C-31-M-12-Hroparts-5A 1 16P Female Type-C SMD USB Connectors ROHS</t>
   </si>
   <si>
     <t>https://robu.in/product/type-c-31-m-12-hroparts-5a-1-16p-female-type-c-smd-usb-connectors-rohs/</t>
+  </si>
+  <si>
+    <t>Free</t>
   </si>
   <si>
     <t>Seeed Studio XIAO RP2040 v1.0</t>
@@ -108,6 +105,9 @@
   <si>
     <t>Total (INR):</t>
   </si>
+  <si>
+    <t>₹ 7,046.70</t>
+  </si>
 </sst>
 </file>
 
@@ -117,7 +117,7 @@
     <numFmt numFmtId="164" formatCode="[$₹]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -132,10 +132,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -156,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -180,10 +176,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -195,6 +191,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -412,7 +411,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="43.88"/>
+    <col customWidth="1" min="1" max="1" width="63.63"/>
     <col customWidth="1" min="4" max="4" width="16.5"/>
     <col customWidth="1" min="6" max="6" width="13.38"/>
   </cols>
@@ -440,73 +439,86 @@
         <v>6</v>
       </c>
       <c r="H1" s="4"/>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="I1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5">
+        <v>220.0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="5">
-        <v>180.0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="7">
         <f t="shared" ref="E2:E4" si="1">B2*C2</f>
-        <v>720</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5">
-        <v>2120.0</v>
+        <v>440</v>
+      </c>
+      <c r="F2" s="8">
+        <v>83.0</v>
+      </c>
+      <c r="G2" s="7">
+        <f t="shared" ref="G2:G4" si="2">E2+F2</f>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5">
-        <v>1000.0</v>
+        <v>10.0</v>
       </c>
       <c r="C3" s="2">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>400</v>
+      </c>
+      <c r="F3" s="9">
+        <v>130.0</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" si="2"/>
+        <v>530</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5">
-        <v>10.0</v>
+        <v>95.0</v>
       </c>
       <c r="C4" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>14</v>
+        <v>8.0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E4" s="7">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>760</v>
+      </c>
+      <c r="F4" s="9">
+        <v>100.0</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="2"/>
+        <v>860</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5">
         <v>38.0</v>
@@ -514,15 +526,15 @@
       <c r="C5" s="2">
         <v>2.0</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="E5" s="7">
-        <f t="shared" ref="E5:E7" si="2">C5*B5</f>
+        <f t="shared" ref="E5:E7" si="3">C5*B5</f>
         <v>76</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
+      <c r="F5" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="G5" s="5">
         <v>1372.0</v>
@@ -530,7 +542,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5">
         <v>618.0</v>
@@ -538,17 +550,17 @@
       <c r="C6" s="2">
         <v>2.0</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>18</v>
+      <c r="D6" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5">
         <v>6.0</v>
@@ -556,17 +568,17 @@
       <c r="C7" s="2">
         <v>10.0</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
+      <c r="D7" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="5">
         <v>1.8</v>
@@ -574,14 +586,14 @@
       <c r="C8" s="2">
         <v>15.0</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>22</v>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E8:E9" si="3">B8*C8</f>
+        <f t="shared" ref="E8:E9" si="4">B8*C8</f>
         <v>27</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>70.0</v>
       </c>
       <c r="G8" s="5">
@@ -590,7 +602,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5">
         <v>4.4</v>
@@ -598,11 +610,11 @@
       <c r="C9" s="2">
         <v>15.0</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
+      <c r="D9" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
     </row>
@@ -614,7 +626,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="12">
         <v>26.17</v>
@@ -622,24 +634,24 @@
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>26</v>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E11" s="13">
         <f>B11*C11</f>
         <v>26.17</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>27</v>
+      <c r="F11" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" ref="G11:G12" si="4">E11</f>
+        <f t="shared" ref="G11:G12" si="5">E11</f>
         <v>26.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="5">
         <v>1094.0</v>
@@ -647,18 +659,18 @@
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>29</v>
+      <c r="D12" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="E12" s="7">
         <f>B12</f>
         <v>1094</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>27</v>
+      <c r="F12" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G12" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1094</v>
       </c>
     </row>
@@ -666,20 +678,20 @@
       <c r="A13" s="10"/>
       <c r="D13" s="10"/>
       <c r="F13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="12">
-        <v>76.17</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10"/>
       <c r="D14" s="10"/>
       <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="G14" s="5">
-        <v>7276.68</v>
       </c>
     </row>
     <row r="15">
@@ -694,10 +706,6 @@
       <c r="A17" s="10"/>
       <c r="D17" s="10"/>
     </row>
-    <row r="18">
-      <c r="A18" s="10"/>
-      <c r="D18" s="10"/>
-    </row>
     <row r="19">
       <c r="A19" s="10"/>
       <c r="D19" s="10"/>
@@ -4627,9 +4635,7 @@
       <c r="D1000" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
+  <mergeCells count="4">
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="F8:F9"/>
